--- a/Planilhas_importação/Importacao_contratos.xlsx
+++ b/Planilhas_importação/Importacao_contratos.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -969,7 +969,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AI1"/>
-  <sheetFormatPr defaultColWidth="11.515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.84"/>

--- a/Planilhas_importação/Importacao_contratos.xlsx
+++ b/Planilhas_importação/Importacao_contratos.xlsx
@@ -296,9 +296,9 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Obrigatório. Informe o tipo do contrato, seguindo uma das nomenclaturas abaixo:
-- Contrato de compra e venda
-- Contrato de compra e venda com financiamento bancário
-- Contrato de compra e venda com pacto de alienação fiduciária</t>
+- CONTRATO DE COMPRA E VENDA
+- CONTRATO DE COMPRA E VENDA COM FINANCIAMENTO BANCARIO
+- CONTRATO DE COMPRA E VENDA COM PACTO DE ALIENACAO FIDUCIARIA</t>
         </r>
       </text>
     </comment>
@@ -312,8 +312,10 @@
           </rPr>
           <t xml:space="preserve">Obrigatório. Informe o indexador utilizado:
 - IPCA
-- IGPM
-- INCC-DI</t>
+- IGP-M
+- INCC-DI
+- INCC-M
+- POUPANCA</t>
         </r>
       </text>
     </comment>
@@ -653,14 +655,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF34B3FB"/>
+        <bgColor rgb="FF00CCFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFD7"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -687,7 +689,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="31">
+  <cellStyleXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -744,6 +746,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -775,7 +780,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="17">
+  <cellStyles count="18">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
@@ -793,6 +798,7 @@
     <cellStyle name="Normal" xfId="28"/>
     <cellStyle name="Título de tabela" xfId="29"/>
     <cellStyle name="Índice" xfId="30"/>
+    <cellStyle name="caption" xfId="31"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -814,8 +820,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFD7"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFBBE6FE"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -837,7 +843,7 @@
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF34B3FB"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>

--- a/Planilhas_importação/Importacao_contratos.xlsx
+++ b/Planilhas_importação/Importacao_contratos.xlsx
@@ -427,6 +427,20 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
+          <t xml:space="preserve">Informe 
+- VALOR_VENDA  
+- VALOR_RECEBIDO</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AF1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">Obrigatório. Caso não tenha sido realizada nenhuma cobrança, este campo deverá ser preenchido com o valor 0,00% (ZERO).
 É o valor que será retido correspondente aos impostos federais recolhidos pela empresa. O percentual configurado será aplicado sobre o valor recebido do cliente.
 Atenção para informar com pelo menos 2 casas decimais após a vírgula.
@@ -434,7 +448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF1" authorId="0">
+    <comment ref="AG1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -449,7 +463,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG1" authorId="0">
+    <comment ref="AH1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -461,7 +475,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH1" authorId="0">
+    <comment ref="AI1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -473,7 +487,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI1" authorId="0">
+    <comment ref="AJ1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -490,7 +504,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t xml:space="preserve">numero_contrato</t>
   </si>
@@ -580,6 +594,9 @@
   </si>
   <si>
     <t xml:space="preserve">distrato_pena_convencional_percentual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">distrato_pena_convencional_aplicacao</t>
   </si>
   <si>
     <t xml:space="preserve">distrato_impostos_federais_percentual</t>
@@ -604,7 +621,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -631,6 +648,13 @@
       <sz val="10"/>
       <name val="Liberation Serif;Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -750,7 +774,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -775,7 +799,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -789,16 +817,16 @@
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
     <cellStyle name="Body Text" xfId="20"/>
     <cellStyle name="Caption" xfId="21"/>
-    <cellStyle name="Caracteres de nota de fim" xfId="22"/>
-    <cellStyle name="Caracteres de nota de rodapé" xfId="23"/>
-    <cellStyle name="Conteúdo da lista" xfId="24"/>
-    <cellStyle name="Conteúdo da tabela" xfId="25"/>
-    <cellStyle name="FollowedHyperlink" xfId="26"/>
-    <cellStyle name="List" xfId="27"/>
-    <cellStyle name="Normal" xfId="28"/>
-    <cellStyle name="Título de tabela" xfId="29"/>
-    <cellStyle name="Índice" xfId="30"/>
-    <cellStyle name="caption" xfId="31"/>
+    <cellStyle name="caption 1" xfId="22"/>
+    <cellStyle name="Caracteres de nota de fim" xfId="23"/>
+    <cellStyle name="Caracteres de nota de rodapé" xfId="24"/>
+    <cellStyle name="Conteúdo da lista" xfId="25"/>
+    <cellStyle name="Conteúdo da tabela" xfId="26"/>
+    <cellStyle name="FollowedHyperlink" xfId="27"/>
+    <cellStyle name="List" xfId="28"/>
+    <cellStyle name="Normal" xfId="29"/>
+    <cellStyle name="Título de tabela" xfId="30"/>
+    <cellStyle name="Índice" xfId="31"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -974,7 +1002,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AI1"/>
+  <dimension ref="A1:AJ1"/>
   <sheetFormatPr defaultColWidth="11.515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.55"/>
@@ -1005,14 +1033,14 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="22.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="18.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="33.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="32.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="24.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="21.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="27.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="23.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="31" style="1" width="32.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="24.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="21.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="27.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="23.12"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1103,13 +1131,13 @@
       <c r="AD1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" s="6" t="s">
         <v>30</v>
       </c>
       <c r="AF1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AG1" s="3" t="s">
         <v>32</v>
       </c>
       <c r="AH1" s="4" t="s">
@@ -1117,6 +1145,9 @@
       </c>
       <c r="AI1" s="4" t="s">
         <v>34</v>
+      </c>
+      <c r="AJ1" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Planilhas_importação/Importacao_contratos.xlsx
+++ b/Planilhas_importação/Importacao_contratos.xlsx
@@ -410,6 +410,23 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
+          <t xml:space="preserve">Obrigatório apenas se o sistema de amortização for SACOC. Informar se a capitalização ocorre na data de emissão ou aniversário:
+- DATA_ANIVERSARIO_ANUAL
+- DATA_ANIVERSARIO_MENSAL
+- EMISSAO_ANUAL
+- EMISSAO_MENSAL
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AE1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">Obrigatório. Caso não tenha sido realizada nenhuma cobrança, este campo deverá ser preenchido com o valor 0,00% (ZERO).
 É o valor que será retido a título de multa em caso de cancelamento contratual por descumprimento de obrigações, ou por iniciativa do cliente.
 Para empreendimentos do tipo loteamento, loteamento de chácara e loteamento fechado com acesso controlado, o percentual configurado será aplicado sobre o valor de venda da unidade. 
@@ -419,7 +436,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE1" authorId="0">
+    <comment ref="AF1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -433,7 +450,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF1" authorId="0">
+    <comment ref="AG1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -448,7 +465,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG1" authorId="0">
+    <comment ref="AH1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -463,7 +480,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH1" authorId="0">
+    <comment ref="AI1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -475,7 +492,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI1" authorId="0">
+    <comment ref="AJ1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -487,7 +504,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ1" authorId="0">
+    <comment ref="AK1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -504,7 +521,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">numero_contrato</t>
   </si>
@@ -591,6 +608,9 @@
   </si>
   <si>
     <t xml:space="preserve">sistema_amortizacao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sacoc_capitalizacao_juros</t>
   </si>
   <si>
     <t xml:space="preserve">distrato_pena_convencional_percentual</t>
@@ -621,7 +641,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -652,6 +672,14 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -670,7 +698,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -681,12 +709,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF34B3FB"/>
         <bgColor rgb="FF00CCFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.8"/>
-        <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -713,7 +735,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="32">
+  <cellStyleXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -773,8 +795,11 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -791,24 +816,28 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="18">
+  <cellStyles count="19">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
@@ -827,6 +856,7 @@
     <cellStyle name="Normal" xfId="29"/>
     <cellStyle name="Título de tabela" xfId="30"/>
     <cellStyle name="Índice" xfId="31"/>
+    <cellStyle name="caption" xfId="32"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -849,7 +879,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFBBE6FE"/>
+      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -1002,7 +1032,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr defaultColWidth="11.515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.55"/>
@@ -1032,15 +1062,15 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="23.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="22.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="18.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="33.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="31" style="1" width="32.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="24.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="21.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="27.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="23.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="30" style="1" width="33.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="32" style="1" width="32.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="24.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="21.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="27.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="23.12"/>
   </cols>
   <sheetData>
-    <row r="1" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1128,19 +1158,19 @@
       <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AE1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="7" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AH1" s="3" t="s">
         <v>33</v>
       </c>
       <c r="AI1" s="4" t="s">
@@ -1148,6 +1178,9 @@
       </c>
       <c r="AJ1" s="4" t="s">
         <v>35</v>
+      </c>
+      <c r="AK1" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
